--- a/experiment/HAT+CNN_2CH_bestx4/Test/results-Urban100/Urban100.xlsx
+++ b/experiment/HAT+CNN_2CH_bestx4/Test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.59</v>
+        <v>27.6</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7672</v>
+        <v>0.7671</v>
       </c>
     </row>
     <row r="3">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.81</v>
+        <v>26.83</v>
       </c>
       <c r="C3" t="n">
         <v>0.8215</v>
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.91</v>
+        <v>23.93</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6919</v>
+        <v>0.6924</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.82</v>
+        <v>23.79</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8451</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>28.11</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9524</v>
+        <v>0.9522</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.47</v>
+        <v>22.45</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6271</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.64</v>
+        <v>29.65</v>
       </c>
       <c r="C8" t="n">
-        <v>0.863</v>
+        <v>0.8631</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         <v>21.52</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6654</v>
+        <v>0.6655</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33.5</v>
+        <v>33.44</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9228</v>
+        <v>0.9213</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.39</v>
+        <v>27.33</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8897</v>
+        <v>0.8882</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.92</v>
+        <v>17.9</v>
       </c>
       <c r="C12" t="n">
-        <v>0.795</v>
+        <v>0.7929</v>
       </c>
     </row>
     <row r="13">
@@ -598,7 +598,7 @@
         <v>23.96</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7389</v>
       </c>
     </row>
     <row r="14">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.68</v>
+        <v>29.69</v>
       </c>
       <c r="C14" t="n">
         <v>0.8421</v>
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.36</v>
+        <v>22.38</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26.31</v>
+        <v>26.32</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7411</v>
+        <v>0.7413</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.29</v>
+        <v>30.17</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.9129</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25.78</v>
+        <v>25.82</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8293</v>
+        <v>0.8300999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26.37</v>
+        <v>26.39</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7146</v>
+        <v>0.7149</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.14</v>
+        <v>22.2</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8189</v>
+        <v>0.8208</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.15</v>
+        <v>22.17</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7209</v>
+        <v>0.7204</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29.69</v>
+        <v>29.74</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7852</v>
+        <v>0.7857</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26.11</v>
+        <v>26.12</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7615</v>
+        <v>0.7609</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.54</v>
+        <v>30.57</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9177</v>
+        <v>0.9177999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.92</v>
+        <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6511</v>
+        <v>0.6518</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.15</v>
+        <v>32.11</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9021</v>
+        <v>0.9016</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.92</v>
+        <v>27.91</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7052</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.4</v>
+        <v>28.41</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7984</v>
+        <v>0.7986</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.5</v>
+        <v>31.51</v>
       </c>
       <c r="C29" t="n">
-        <v>0.879</v>
+        <v>0.8793</v>
       </c>
     </row>
     <row r="30">
@@ -819,7 +819,7 @@
         <v>27.47</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8759</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24.45</v>
+        <v>24.54</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8057</v>
+        <v>0.8075</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24.35</v>
+        <v>24.36</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7951</v>
+        <v>0.7956</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.28</v>
+        <v>29.23</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8599</v>
+        <v>0.8584000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27.5</v>
+        <v>27.52</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8126</v>
+        <v>0.8116</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>23.09</v>
+        <v>23.08</v>
       </c>
       <c r="C35" t="n">
-        <v>0.588</v>
+        <v>0.5878</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.07</v>
+        <v>28.98</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8794</v>
+        <v>0.8784999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28.88</v>
+        <v>28.89</v>
       </c>
       <c r="C37" t="n">
         <v>0.8868</v>
@@ -923,7 +923,7 @@
         <v>26.56</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8033</v>
+        <v>0.8034</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>27.07</v>
+        <v>27.04</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6864</v>
+        <v>0.6844</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         <v>23.08</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7471</v>
+        <v>0.7459</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27.15</v>
+        <v>27.04</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9424</v>
+        <v>0.9419</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.54</v>
+        <v>26.58</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8889</v>
+        <v>0.8897</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.54</v>
+        <v>28.56</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8834</v>
+        <v>0.8838</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32.52</v>
+        <v>32.57</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9374</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.71</v>
+        <v>31.72</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.8653</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>23.89</v>
+        <v>23.69</v>
       </c>
       <c r="C46" t="n">
-        <v>0.704</v>
+        <v>0.6934</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.66</v>
+        <v>23.65</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7625</v>
+        <v>0.7614</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21.69</v>
+        <v>21.71</v>
       </c>
       <c r="C48" t="n">
-        <v>0.77</v>
+        <v>0.7698</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.28</v>
+        <v>20.25</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8172</v>
+        <v>0.8167</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.69</v>
+        <v>23.7</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7581</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25.37</v>
+        <v>25.39</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7766</v>
+        <v>0.7769</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>27.42</v>
+        <v>27.44</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8501</v>
+        <v>0.8504</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28.93</v>
+        <v>28.9</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9093</v>
+        <v>0.9095</v>
       </c>
     </row>
     <row r="54">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>21.2</v>
+        <v>21.21</v>
       </c>
       <c r="C55" t="n">
-        <v>0.653</v>
+        <v>0.6528</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>33.38</v>
+        <v>33.42</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9489</v>
+        <v>0.9497</v>
       </c>
     </row>
     <row r="57">
@@ -1170,7 +1170,7 @@
         <v>25.06</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7864</v>
+        <v>0.7866</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.2</v>
+        <v>31.21</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8991</v>
+        <v>0.8994</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25.87</v>
+        <v>25.84</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.8604000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>22.24</v>
+        <v>22.3</v>
       </c>
       <c r="C60" t="n">
-        <v>0.77</v>
+        <v>0.7716</v>
       </c>
     </row>
     <row r="61">
@@ -1222,7 +1222,7 @@
         <v>22.62</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5727</v>
+        <v>0.5719</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24.76</v>
+        <v>24.75</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7621</v>
+        <v>0.7618</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>21.92</v>
+        <v>21.84</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8171</v>
+        <v>0.8156</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.48</v>
+        <v>22.47</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6213</v>
+        <v>0.6216</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>26.5</v>
+        <v>26.56</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7819</v>
+        <v>0.7833</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.41</v>
+        <v>25.4</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7238</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>22.21</v>
+        <v>22.22</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6418</v>
+        <v>0.6424</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>19.79</v>
+        <v>19.83</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8815</v>
+        <v>0.8819</v>
       </c>
     </row>
     <row r="69">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30.51</v>
+        <v>30.55</v>
       </c>
       <c r="C69" t="n">
         <v>0.8899</v>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>24.76</v>
+        <v>24.78</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7539</v>
+        <v>0.7544999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -1352,7 +1352,7 @@
         <v>22.18</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5994</v>
+        <v>0.5987</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>28.09</v>
+        <v>28.08</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6732</v>
+        <v>0.6719000000000001</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>20.04</v>
+        <v>20.09</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8188</v>
+        <v>0.8195</v>
       </c>
     </row>
     <row r="74">
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>20.07</v>
+        <v>20.1</v>
       </c>
       <c r="C74" t="n">
         <v>0.5741000000000001</v>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23.79</v>
+        <v>23.85</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7176</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="76">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31.71</v>
+        <v>31.72</v>
       </c>
       <c r="C76" t="n">
         <v>0.8868</v>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>23.09</v>
+        <v>23</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7439</v>
+        <v>0.7388</v>
       </c>
     </row>
     <row r="78">
@@ -1443,7 +1443,7 @@
         <v>22.74</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6773</v>
+        <v>0.6768999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>27.32</v>
+        <v>27.36</v>
       </c>
       <c r="C79" t="n">
-        <v>0.774</v>
+        <v>0.7748</v>
       </c>
     </row>
     <row r="80">
@@ -1469,7 +1469,7 @@
         <v>25.5</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6986</v>
+        <v>0.6984</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.66</v>
+        <v>35.61</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9534</v>
+        <v>0.9529</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>37.97</v>
+        <v>38.02</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9746</v>
+        <v>0.9748</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9429</v>
+        <v>0.9428</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.28</v>
+        <v>22.29</v>
       </c>
       <c r="C84" t="n">
-        <v>0.7036</v>
+        <v>0.7033</v>
       </c>
     </row>
     <row r="85">
@@ -1534,7 +1534,7 @@
         <v>28.75</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8129</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>28.32</v>
+        <v>28.31</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9039</v>
+        <v>0.9036</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>30.41</v>
+        <v>30.46</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8865</v>
+        <v>0.8853</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.78</v>
+        <v>27.85</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8864</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>19.86</v>
+        <v>19.88</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5719</v>
+        <v>0.5723</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>26.77</v>
+        <v>26.79</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7186</v>
+        <v>0.7188</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37.86</v>
+        <v>37.89</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9762</v>
+        <v>0.9761</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>23.93</v>
+        <v>23.96</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6803</v>
+        <v>0.6805</v>
       </c>
     </row>
     <row r="93">
@@ -1638,7 +1638,7 @@
         <v>18.96</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6587</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>29.26</v>
+        <v>29.13</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9298</v>
+        <v>0.9288999999999999</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>27.18</v>
+        <v>27.17</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7852</v>
+        <v>0.7845</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20.01</v>
+        <v>20</v>
       </c>
       <c r="C96" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>24.87</v>
+        <v>24.9</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8647</v>
+        <v>0.8648</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>24.92</v>
+        <v>24.94</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7654</v>
+        <v>0.7657</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>20.76</v>
+        <v>20.77</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5393</v>
+        <v>0.5391</v>
       </c>
     </row>
     <row r="100">
@@ -1729,7 +1729,7 @@
         <v>25.94</v>
       </c>
       <c r="C100" t="n">
-        <v>0.8057</v>
+        <v>0.8065</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>26.38</v>
+        <v>26.37</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.7512</v>
       </c>
     </row>
     <row r="102">
@@ -1755,7 +1755,7 @@
         <v>26.08</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7867</v>
+        <v>0.7864</v>
       </c>
     </row>
   </sheetData>
